--- a/data/gravel/Otso Waheela (short) 2025.xlsx
+++ b/data/gravel/Otso Waheela (short) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABFD7C8-FCF9-0946-A9A6-8143C107AEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50DF0AC-CBF3-944E-BB9E-8C3E46B8F9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9280" yWindow="1620" windowWidth="24700" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25760" yWindow="-18000" windowWidth="24700" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t>usd</t>
+  </si>
+  <si>
+    <t>https://otsocycles.com/cdn/shop/files/WaheelaC_Sparkle_Side.jpg?v=1758133767&amp;width=4096</t>
   </si>
 </sst>
 </file>
@@ -738,7 +741,7 @@
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -754,7 +757,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -762,7 +765,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -770,7 +773,7 @@
         <v>45907</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -778,7 +781,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -786,7 +794,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -804,7 +812,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -824,7 +832,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>95</v>
       </c>
@@ -844,7 +852,7 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -864,7 +872,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -884,7 +892,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>96</v>
       </c>
@@ -904,7 +912,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -925,7 +933,7 @@
       </c>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -933,23 +941,35 @@
         <v>20</v>
       </c>
       <c r="C15" s="2">
-        <f>VALUE(LEFT(G17,2))</f>
+        <f>VALUE(LEFT(G15,2))</f>
         <v>68</v>
       </c>
       <c r="D15" s="2">
-        <f>VALUE(LEFT(H17,2))</f>
+        <f>VALUE(LEFT(H15,2))</f>
         <v>68</v>
       </c>
       <c r="E15" s="2">
-        <f>VALUE(LEFT(I17,2))</f>
+        <f>VALUE(LEFT(I15,2))</f>
         <v>68</v>
       </c>
       <c r="F15" s="2">
-        <f>VALUE(LEFT(J17,2))</f>
+        <f>VALUE(LEFT(J15,2))</f>
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G15" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -957,20 +977,32 @@
         <v>22</v>
       </c>
       <c r="C16" s="2">
-        <f>VALUE(LEFT(G18,3))</f>
+        <f>VALUE(LEFT(G16,3))</f>
         <v>420</v>
       </c>
       <c r="D16" s="2">
-        <f>VALUE(LEFT(H18,3))</f>
+        <f>VALUE(LEFT(H16,3))</f>
         <v>420</v>
       </c>
       <c r="E16" s="2">
-        <f>VALUE(LEFT(I18,3))</f>
+        <f>VALUE(LEFT(I16,3))</f>
         <v>420</v>
       </c>
       <c r="F16" s="2">
-        <f>VALUE(LEFT(J18,3))</f>
+        <f>VALUE(LEFT(J16,3))</f>
         <v>420</v>
+      </c>
+      <c r="G16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -981,32 +1013,32 @@
         <v>24</v>
       </c>
       <c r="C17" s="2">
-        <f>VALUE(LEFT(G19,4))</f>
+        <f>VALUE(LEFT(G17,4))</f>
         <v>1008</v>
       </c>
       <c r="D17" s="2">
-        <f>VALUE(LEFT(H19,4))</f>
+        <f>VALUE(LEFT(H17,4))</f>
         <v>1015</v>
       </c>
       <c r="E17" s="2">
-        <f>VALUE(LEFT(I19,4))</f>
+        <f>VALUE(LEFT(I17,4))</f>
         <v>1039</v>
       </c>
       <c r="F17" s="2">
-        <f>VALUE(LEFT(J19,4))</f>
+        <f>VALUE(LEFT(J17,4))</f>
         <v>1062</v>
       </c>
       <c r="G17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="I17" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="J17" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -1028,18 +1060,6 @@
       <c r="F18">
         <v>68</v>
       </c>
-      <c r="G18" t="s">
-        <v>94</v>
-      </c>
-      <c r="H18" t="s">
-        <v>94</v>
-      </c>
-      <c r="I18" t="s">
-        <v>94</v>
-      </c>
-      <c r="J18" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -1060,18 +1080,6 @@
       <c r="F19">
         <v>47</v>
       </c>
-      <c r="G19" t="s">
-        <v>112</v>
-      </c>
-      <c r="H19" t="s">
-        <v>113</v>
-      </c>
-      <c r="I19" t="s">
-        <v>114</v>
-      </c>
-      <c r="J19" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -1287,7 +1295,7 @@
         <v>157.47999999999999</v>
       </c>
       <c r="D33">
-        <f t="shared" ref="D33:H33" si="2">D35*2.54</f>
+        <f t="shared" ref="D33:F33" si="2">D35*2.54</f>
         <v>170.18</v>
       </c>
       <c r="E33">
@@ -1308,7 +1316,7 @@
         <v>170.18</v>
       </c>
       <c r="D34">
-        <f t="shared" ref="D34:H34" si="3">D36*2.54</f>
+        <f t="shared" ref="D34:F34" si="3">D36*2.54</f>
         <v>180.34</v>
       </c>
       <c r="E34">

--- a/data/gravel/Otso Waheela (short) 2025.xlsx
+++ b/data/gravel/Otso Waheela (short) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50DF0AC-CBF3-944E-BB9E-8C3E46B8F9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B4D260-3F75-DB43-90FC-84FF1CC8373B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25760" yWindow="-18000" windowWidth="24700" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15400" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -392,10 +392,16 @@
     <t>carbon</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>https://otsocycles.com/cdn/shop/files/WaheelaC_Sparkle_Side.jpg?v=1758133767&amp;width=4096</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Burnsville, Minnesota, USA</t>
   </si>
 </sst>
 </file>
@@ -735,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -783,7 +789,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1655,23 +1661,28 @@
         <v>80</v>
       </c>
       <c r="B72">
-        <v>2575</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>81</v>
       </c>
-      <c r="B73">
-        <v>3800</v>
-      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>82</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>121</v>
+      </c>
+      <c r="B75" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Otso Waheela (short) 2025.xlsx
+++ b/data/gravel/Otso Waheela (short) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B4D260-3F75-DB43-90FC-84FF1CC8373B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80108B02-4EC7-5A48-B094-68379C61D182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15400" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -402,6 +402,24 @@
   </si>
   <si>
     <t>Burnsville, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -741,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1502,186 +1520,216 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53">
-        <v>30.9</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>63</v>
-      </c>
-      <c r="B55">
-        <v>50</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56">
-        <v>53</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>59</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58">
-        <v>160</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B59">
+        <v>30.9</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>90</v>
+        <v>63</v>
+      </c>
+      <c r="B61">
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B62">
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B63">
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
+        <v>69</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B71">
-        <v>2700</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72">
-        <v>3800</v>
+        <v>74</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="B73">
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>121</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>122</v>
       </c>
     </row>
